--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0003T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.863346867874704</v>
+        <v>1.602793866029639</v>
       </c>
       <c r="D2" t="n">
-        <v>9.407863201816275</v>
+        <v>1.528777770295145</v>
       </c>
       <c r="E2" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F2" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.03663977214319</v>
+        <v>5.368453962973269</v>
       </c>
       <c r="D3" t="n">
-        <v>33.05257789943656</v>
+        <v>5.37104390865844</v>
       </c>
       <c r="E3" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F3" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.67522653428951</v>
+        <v>5.797224311822046</v>
       </c>
       <c r="D4" t="n">
-        <v>36.02276659170554</v>
+        <v>5.85369957115215</v>
       </c>
       <c r="E4" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F4" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.08478796353358</v>
+        <v>3.263778044074207</v>
       </c>
       <c r="D5" t="n">
-        <v>20.38039469903963</v>
+        <v>3.31181413859394</v>
       </c>
       <c r="E5" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F5" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.47148610920831</v>
+        <v>4.464116492746351</v>
       </c>
       <c r="D6" t="n">
-        <v>27.05531300452563</v>
+        <v>4.396488363235415</v>
       </c>
       <c r="E6" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F6" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.96466921475273</v>
+        <v>5.844258747397319</v>
       </c>
       <c r="D7" t="n">
-        <v>35.49442860496952</v>
+        <v>5.767844648307547</v>
       </c>
       <c r="E7" t="n">
-        <v>9.431963965776035</v>
+        <v>1.532694144438606</v>
       </c>
       <c r="F7" t="n">
-        <v>9.517067857628982</v>
+        <v>1.54652352686471</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
